--- a/Data/Regression Evidence 2025/Workday_NewHire_UKNI_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_UKNI_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E2A09A-6949-4C5B-ACC6-273ADCBD0AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C866912A-3A72-4E44-B045-FBEED9231E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,10 +222,10 @@
     <t>Mr.</t>
   </si>
   <si>
-    <t>Ila</t>
-  </si>
-  <si>
-    <t>Dickens</t>
+    <t>Barry</t>
+  </si>
+  <si>
+    <t>Runolfsson</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -306,7 +306,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB923135A</t>
+    <t>AB923148A</t>
   </si>
   <si>
     <t>Male</t>
@@ -342,13 +342,13 @@
     <t>519 Store Management (Fozac Hosoti (9575064))</t>
   </si>
   <si>
-    <t>Griffin</t>
-  </si>
-  <si>
-    <t>Grant</t>
-  </si>
-  <si>
-    <t>Auto 67794496</t>
+    <t>Wilber</t>
+  </si>
+  <si>
+    <t>Kuvalis</t>
+  </si>
+  <si>
+    <t>Auto 30608985</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -360,7 +360,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB923136A</t>
+    <t>AB923149A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -376,7 +376,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,14 +444,6 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -550,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -630,7 +622,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1168,9 +1159,9 @@
         <v>59</v>
       </c>
       <c r="B2" s="8">
-        <v>10700265</v>
-      </c>
-      <c r="C2" s="32" t="s">
+        <v>10700464</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>111</v>
       </c>
       <c r="D2" s="9" t="s">
@@ -1199,7 +1190,7 @@
       </c>
       <c r="L2" s="15">
         <f ca="1">TODAY()-30</f>
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>61</v>
@@ -1236,11 +1227,11 @@
       </c>
       <c r="X2" s="15">
         <f ca="1">TODAY()-30</f>
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="Y2" s="18">
         <f t="shared" ref="Y2:Y3" ca="1" si="0">X2+90</f>
-        <v>45913</v>
+        <v>45934</v>
       </c>
       <c r="Z2" s="14" t="s">
         <v>76</v>
@@ -1359,9 +1350,9 @@
         <v>101</v>
       </c>
       <c r="B3" s="8">
-        <v>10700266</v>
-      </c>
-      <c r="C3" s="32" t="s">
+        <v>10700465</v>
+      </c>
+      <c r="C3" s="31" t="s">
         <v>111</v>
       </c>
       <c r="D3" s="9" t="s">
@@ -1390,7 +1381,7 @@
       </c>
       <c r="L3" s="15">
         <f ca="1">TODAY()-30</f>
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>61</v>
@@ -1427,11 +1418,11 @@
       </c>
       <c r="X3" s="15">
         <f ca="1">TODAY()-30</f>
-        <v>45823</v>
+        <v>45844</v>
       </c>
       <c r="Y3" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>45913</v>
+        <v>45934</v>
       </c>
       <c r="Z3" s="14" t="s">
         <v>76</v>
@@ -1561,6 +1552,6 @@
     <hyperlink ref="AI3" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId5"/>
 </worksheet>
 </file>